--- a/Result/profitability/3236.xlsx
+++ b/Result/profitability/3236.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04750000000000003</v>
+        <v>0.06875000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>24.17625</v>
+        <v>24.2725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05875000000000002</v>
+        <v>0.05750000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>23.665</v>
+        <v>24.12875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07500000000000002</v>
+        <v>0.08875000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>23.47375</v>
+        <v>23.75625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04250000000000002</v>
+        <v>0.08000000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>22.79625</v>
+        <v>23.22</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05000000000000003</v>
+        <v>0.02500000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>21.83375</v>
+        <v>21.495</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.004999999999999977</v>
+        <v>-0.01624999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>20.10625</v>
+        <v>20.09</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006250000000000019</v>
+        <v>0.007500000000000017</v>
       </c>
       <c r="N8" t="n">
-        <v>20.15</v>
+        <v>20.53875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07375000000000002</v>
+        <v>0.07375000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>19.8875</v>
@@ -1772,7 +1772,7 @@
         <v>0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0.09750000000000003</v>
+        <v>0.09750000000000002</v>
       </c>
       <c r="N11" t="n">
         <v>19.65625</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>623</v>
+      </c>
+      <c r="D75" t="n">
+        <v>462</v>
+      </c>
+      <c r="E75" t="n">
+        <v>161</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>41</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07375000000000004</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.109999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1364633611232997</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.578947368421053</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.389999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.150599733451799</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
